--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.02304251562731821</v>
       </c>
       <c r="C2" t="n">
-        <v>111829896</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>111829896</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>75814829</v>
+        <v>4072488</v>
       </c>
       <c r="L2" t="n">
-        <v>42817997</v>
+        <v>2186102</v>
       </c>
       <c r="M2" t="n">
-        <v>10636949</v>
+        <v>521233</v>
       </c>
       <c r="N2" t="n">
-        <v>571778</v>
+        <v>23707</v>
       </c>
       <c r="O2" t="n">
-        <v>6443373</v>
+        <v>327292</v>
       </c>
       <c r="P2" t="n">
-        <v>2644186</v>
+        <v>139246</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.99991774559021</v>
+        <v>0.9999029636383057</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8587164282798767</v>
+        <v>0.8302797079086304</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7283568382263184</v>
+        <v>0.6690024733543396</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6451640725135803</v>
+        <v>0.5701065063476562</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4671045541763306</v>
+        <v>0.3499188125133514</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7023639678955078</v>
+        <v>0.6421998143196106</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7626046538352966</v>
+        <v>0.7226163148880005</v>
       </c>
       <c r="X2" t="n">
-        <v>111829896</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>111829896</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>73922569</v>
+        <v>3984507</v>
       </c>
       <c r="AG2" t="n">
-        <v>39658380</v>
+        <v>2036603</v>
       </c>
       <c r="AH2" t="n">
-        <v>9677880</v>
+        <v>481192</v>
       </c>
       <c r="AI2" t="n">
-        <v>529912</v>
+        <v>22644</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5929784</v>
+        <v>303181</v>
       </c>
       <c r="AK2" t="n">
-        <v>2488159</v>
+        <v>131107</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8317187428474426</v>
+        <v>0.8069498538970947</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6876353025436401</v>
+        <v>0.6356266140937805</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5805586576461792</v>
+        <v>0.5195851922035217</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3331095576286316</v>
+        <v>0.2562175989151001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6484201550483704</v>
+        <v>0.5967495441436768</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7152484059333801</v>
+        <v>0.6783864498138428</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.005986791724320211</v>
       </c>
       <c r="C3" t="n">
-        <v>2814</v>
+        <v>165</v>
       </c>
       <c r="D3" t="n">
-        <v>75814829</v>
+        <v>4072488</v>
       </c>
       <c r="E3" t="n">
-        <v>11357389</v>
+        <v>770995</v>
       </c>
       <c r="F3" t="n">
-        <v>618907</v>
+        <v>33472</v>
       </c>
       <c r="G3" t="n">
-        <v>77758</v>
+        <v>4904</v>
       </c>
       <c r="H3" t="n">
-        <v>58140</v>
+        <v>2040</v>
       </c>
       <c r="I3" t="n">
-        <v>9390</v>
+        <v>187</v>
       </c>
       <c r="J3" t="n">
-        <v>177428102</v>
+        <v>9857025</v>
       </c>
       <c r="K3" t="n">
-        <v>188854251</v>
+        <v>10353678</v>
       </c>
       <c r="L3" t="n">
-        <v>214849883</v>
+        <v>11740374</v>
       </c>
       <c r="M3" t="n">
-        <v>266626321</v>
+        <v>14744426</v>
       </c>
       <c r="N3" t="n">
-        <v>287015226</v>
+        <v>15937520</v>
       </c>
       <c r="O3" t="n">
-        <v>277359768</v>
+        <v>15378308</v>
       </c>
       <c r="P3" t="n">
-        <v>284961457</v>
+        <v>15823509</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8621275424957275</v>
+        <v>0.8337998986244202</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7325802445411682</v>
+        <v>0.672973096370697</v>
       </c>
       <c r="T3" t="n">
-        <v>0.63350510597229</v>
+        <v>0.5587029457092285</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3574367463588715</v>
+        <v>0.2668595314025879</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7021244764328003</v>
+        <v>0.6420738101005554</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7592519521713257</v>
+        <v>0.7198407649993896</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>73922569</v>
+        <v>3984507</v>
       </c>
       <c r="Z3" t="n">
-        <v>12795138</v>
+        <v>830301</v>
       </c>
       <c r="AA3" t="n">
-        <v>863205</v>
+        <v>49557</v>
       </c>
       <c r="AB3" t="n">
-        <v>266371</v>
+        <v>16367</v>
       </c>
       <c r="AC3" t="n">
-        <v>78098</v>
+        <v>3146</v>
       </c>
       <c r="AD3" t="n">
-        <v>13846</v>
+        <v>373</v>
       </c>
       <c r="AE3" t="n">
-        <v>177437304</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>186371258</v>
+        <v>10232918</v>
       </c>
       <c r="AG3" t="n">
-        <v>212803814</v>
+        <v>11654492</v>
       </c>
       <c r="AH3" t="n">
-        <v>265484508</v>
+        <v>14692550</v>
       </c>
       <c r="AI3" t="n">
-        <v>286606646</v>
+        <v>15915829</v>
       </c>
       <c r="AJ3" t="n">
-        <v>276875045</v>
+        <v>15355785</v>
       </c>
       <c r="AK3" t="n">
-        <v>284794005</v>
+        <v>15814804</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8406097292900085</v>
+        <v>0.8157867193222046</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6785218119621277</v>
+        <v>0.6269510984420776</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5763858556747437</v>
+        <v>0.5157835483551025</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3312649726867676</v>
+        <v>0.2548937797546387</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6461594700813293</v>
+        <v>0.5947734117507935</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7144502997398376</v>
+        <v>0.6777657270431519</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.05922733603598913</v>
       </c>
       <c r="C4" t="n">
-        <v>1089</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>11559450</v>
+        <v>786124</v>
       </c>
       <c r="E4" t="n">
-        <v>42817997</v>
+        <v>2186102</v>
       </c>
       <c r="F4" t="n">
-        <v>3364860</v>
+        <v>234166</v>
       </c>
       <c r="G4" t="n">
-        <v>137180</v>
+        <v>9125</v>
       </c>
       <c r="H4" t="n">
-        <v>494804</v>
+        <v>29343</v>
       </c>
       <c r="I4" t="n">
-        <v>72820</v>
+        <v>3498</v>
       </c>
       <c r="J4" t="n">
-        <v>9202</v>
+        <v>603</v>
       </c>
       <c r="K4" t="n">
-        <v>12473722</v>
+        <v>832471</v>
       </c>
       <c r="L4" t="n">
-        <v>15969117</v>
+        <v>1081602</v>
       </c>
       <c r="M4" t="n">
-        <v>5850251</v>
+        <v>393040</v>
       </c>
       <c r="N4" t="n">
-        <v>652312</v>
+        <v>44043</v>
       </c>
       <c r="O4" t="n">
-        <v>2730465</v>
+        <v>182350</v>
       </c>
       <c r="P4" t="n">
-        <v>823123</v>
+        <v>53451</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999958872795105</v>
+        <v>0.9999514818191528</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8604185581207275</v>
+        <v>0.8320360779762268</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7304624319076538</v>
+        <v>0.6709819436073303</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6392814517021179</v>
+        <v>0.5643471479415894</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4049774706363678</v>
+        <v>0.3027965128421783</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7022441625595093</v>
+        <v>0.642136812210083</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7609246373176575</v>
+        <v>0.7212258577346802</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>13794059</v>
+        <v>892487</v>
       </c>
       <c r="Z4" t="n">
-        <v>39658380</v>
+        <v>2036603</v>
       </c>
       <c r="AA4" t="n">
-        <v>4014229</v>
+        <v>259401</v>
       </c>
       <c r="AB4" t="n">
-        <v>271194</v>
+        <v>16989</v>
       </c>
       <c r="AC4" t="n">
-        <v>615075</v>
+        <v>37896</v>
       </c>
       <c r="AD4" t="n">
-        <v>95263</v>
+        <v>5048</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>14956715</v>
+        <v>953231</v>
       </c>
       <c r="AG4" t="n">
-        <v>18015186</v>
+        <v>1167484</v>
       </c>
       <c r="AH4" t="n">
-        <v>6992064</v>
+        <v>444916</v>
       </c>
       <c r="AI4" t="n">
-        <v>1060892</v>
+        <v>65734</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3215188</v>
+        <v>204873</v>
       </c>
       <c r="AK4" t="n">
-        <v>990575</v>
+        <v>62156</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8361405730247498</v>
+        <v>0.8113442063331604</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6830481886863708</v>
+        <v>0.631259024143219</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5784647464752197</v>
+        <v>0.517677366733551</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3321847021579742</v>
+        <v>0.2555539906024933</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6472878456115723</v>
+        <v>0.5957598090171814</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7148491740226746</v>
+        <v>0.678075909614563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1731</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>641574</v>
+        <v>31742</v>
       </c>
       <c r="E5" t="n">
-        <v>3731289</v>
+        <v>257584</v>
       </c>
       <c r="F5" t="n">
-        <v>10636949</v>
+        <v>521233</v>
       </c>
       <c r="G5" t="n">
-        <v>239023</v>
+        <v>16461</v>
       </c>
       <c r="H5" t="n">
-        <v>1358233</v>
+        <v>94451</v>
       </c>
       <c r="I5" t="n">
-        <v>181829</v>
+        <v>11341</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12124398</v>
+        <v>811763</v>
       </c>
       <c r="L5" t="n">
-        <v>15630203</v>
+        <v>1062322</v>
       </c>
       <c r="M5" t="n">
-        <v>6153679</v>
+        <v>411701</v>
       </c>
       <c r="N5" t="n">
-        <v>1027884</v>
+        <v>65130</v>
       </c>
       <c r="O5" t="n">
-        <v>2733594</v>
+        <v>182450</v>
       </c>
       <c r="P5" t="n">
-        <v>838434</v>
+        <v>54194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999681711196899</v>
+        <v>0.9999624490737915</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9149640202522278</v>
+        <v>0.8976855874061584</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8907607793807983</v>
+        <v>0.86659175157547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9585022926330566</v>
+        <v>0.9499239921569824</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9941915273666382</v>
+        <v>0.9932065606117249</v>
       </c>
       <c r="V5" t="n">
-        <v>0.981110692024231</v>
+        <v>0.9772998690605164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9942559599876404</v>
+        <v>0.9933016896247864</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>820688</v>
+        <v>43217</v>
       </c>
       <c r="Z5" t="n">
-        <v>4187094</v>
+        <v>272950</v>
       </c>
       <c r="AA5" t="n">
-        <v>9677880</v>
+        <v>481192</v>
       </c>
       <c r="AB5" t="n">
-        <v>293448</v>
+        <v>18183</v>
       </c>
       <c r="AC5" t="n">
-        <v>1585798</v>
+        <v>102950</v>
       </c>
       <c r="AD5" t="n">
-        <v>225720</v>
+        <v>14442</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>14016658</v>
+        <v>899744</v>
       </c>
       <c r="AG5" t="n">
-        <v>18789820</v>
+        <v>1211821</v>
       </c>
       <c r="AH5" t="n">
-        <v>7112748</v>
+        <v>451742</v>
       </c>
       <c r="AI5" t="n">
-        <v>1069750</v>
+        <v>66193</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3247183</v>
+        <v>206561</v>
       </c>
       <c r="AK5" t="n">
-        <v>994461</v>
+        <v>62333</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8998387455940247</v>
+        <v>0.8846964240074158</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8727646470069885</v>
+        <v>0.8519448637962341</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9512395262718201</v>
+        <v>0.9442043900489807</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9926343560218811</v>
+        <v>0.9917907118797302</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9776595234870911</v>
+        <v>0.9743980169296265</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9931377172470093</v>
+        <v>0.9922535419464111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2435</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>204260</v>
+        <v>13284</v>
       </c>
       <c r="E6" t="n">
-        <v>284696</v>
+        <v>18724</v>
       </c>
       <c r="F6" t="n">
-        <v>323838</v>
+        <v>18721</v>
       </c>
       <c r="G6" t="n">
-        <v>571778</v>
+        <v>23707</v>
       </c>
       <c r="H6" t="n">
-        <v>181842</v>
+        <v>12124</v>
       </c>
       <c r="I6" t="n">
-        <v>30813</v>
+        <v>2093</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>243195</v>
+        <v>14535</v>
       </c>
       <c r="Z6" t="n">
-        <v>285351</v>
+        <v>18407</v>
       </c>
       <c r="AA6" t="n">
-        <v>303552</v>
+        <v>18577</v>
       </c>
       <c r="AB6" t="n">
-        <v>529912</v>
+        <v>22644</v>
       </c>
       <c r="AC6" t="n">
-        <v>201699</v>
+        <v>12340</v>
       </c>
       <c r="AD6" t="n">
-        <v>35953</v>
+        <v>2334</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>708</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>63654</v>
+        <v>1259</v>
       </c>
       <c r="E7" t="n">
-        <v>540617</v>
+        <v>32066</v>
       </c>
       <c r="F7" t="n">
-        <v>1425181</v>
+        <v>100649</v>
       </c>
       <c r="G7" t="n">
-        <v>175163</v>
+        <v>12104</v>
       </c>
       <c r="H7" t="n">
-        <v>6443373</v>
+        <v>327292</v>
       </c>
       <c r="I7" t="n">
-        <v>528271</v>
+        <v>36332</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>90797</v>
+        <v>2906</v>
       </c>
       <c r="Z7" t="n">
-        <v>675869</v>
+        <v>42232</v>
       </c>
       <c r="AA7" t="n">
-        <v>1660197</v>
+        <v>109140</v>
       </c>
       <c r="AB7" t="n">
-        <v>200527</v>
+        <v>12324</v>
       </c>
       <c r="AC7" t="n">
-        <v>5929784</v>
+        <v>303181</v>
       </c>
       <c r="AD7" t="n">
-        <v>619793</v>
+        <v>39959</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>425</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>4784</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>55126</v>
+        <v>2233</v>
       </c>
       <c r="F8" t="n">
-        <v>117465</v>
+        <v>6032</v>
       </c>
       <c r="G8" t="n">
-        <v>23188</v>
+        <v>1449</v>
       </c>
       <c r="H8" t="n">
-        <v>637446</v>
+        <v>44392</v>
       </c>
       <c r="I8" t="n">
-        <v>2644186</v>
+        <v>139246</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7976</v>
+        <v>86</v>
       </c>
       <c r="Z8" t="n">
-        <v>71734</v>
+        <v>3594</v>
       </c>
       <c r="AA8" t="n">
-        <v>150881</v>
+        <v>8241</v>
       </c>
       <c r="AB8" t="n">
-        <v>29352</v>
+        <v>1871</v>
       </c>
       <c r="AC8" t="n">
-        <v>734518</v>
+        <v>48541</v>
       </c>
       <c r="AD8" t="n">
-        <v>2488159</v>
+        <v>131107</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
